--- a/restructuration-sfe/ig/StructureDefinition-fr-patient.xlsx
+++ b/restructuration-sfe/ig/StructureDefinition-fr-patient.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-31T07:50:12+00:00</t>
+    <t>2026-07-31T12:42:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
